--- a/Report/text002.summary.xlsx
+++ b/Report/text002.summary.xlsx
@@ -453,12 +453,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>["Open 'https://www.netflix.com'", "Click 'Sign In' button", "Fill 'testuser@example.com' into Email field", "Fill 'Test@1234' into Password field", "Submit login form", "Verify redirection to 'https://www.netflix.com/browse' within 3 seconds", "Verify at least 5 personalized movie thumbnails are displayed", "Verify font of all input fields is 'Roboto 16px'", "Verify padding of all input fields is '12px'", "Verify margin-bottom of all input fields is '16px'", "Verify background color of 'Sign In' button is '#e50914'", "Verify text color of 'Sign In' button is '#ffffff'", "Verify border radius of 'Sign In' button is '4px'", "Verify 'Sign In' button is responsive down to 360px screen width", "Verify all elements meet WCAG contrast ratio of at least 4.5:1"]</t>
+          <t>["Open 'https://www.netflix.com'", "Click on the 'Sign In' button located at the top-right corner (within 50px from top and 30px from right)", "Fill 'testuser@example.com' into the email input field", "Fill 'Test@1234' into the password input field", "Submit the login form", "Verify that after submission the user is redirected to 'https://www.netflix.com/browse' within 3 seconds", "Check that the page displays at least 5 personalized movie thumbnails", "Verify that all input fields have font 'Roboto 16px', padding '12px', and margin-bottom '16px'", "Verify that the 'Sign In' button has background color '#e50914', text color '#ffffff', and border radius '4px'", "Verify that the 'Sign In' button is responsive down to 360px screen width", "Verify that all visible elements meet WCAG contrast ratio of at least 4.5:1"]</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>[{"action": "interact", "selector": "url", "value": "https://www.netflix.com", "expected": {}}, {"action": "locate", "selector": "Sign In button", "value": "", "expected": {}}, {"action": "interact", "selector": "Sign In button", "value": "", "expected": {}}, {"action": "locate", "selector": "Email field", "value": "", "expected": {}}, {"action": "interact", "selector": "Email field", "value": "testuser@example.com", "expected": {}}, {"action": "locate", "selector": "password field", "value": "", "expected": {}}, {"action": "interact", "selector": "password field", "value": "Test@1234", "expected": {}}, {"action": "interact", "selector": "button[type='submit']", "value": "", "expected": {}}, {"action": "verify", "selector": "url", "value": "", "expected": {"property": "href", "value": "https://www.netflix.com/browse", "relation": "equal"}}, {"action": "verify", "selector": "url", "value": "", "expected": {"property": "loading_time", "value": "3", "relation": "less_than_or_equal"}}, {"action": "locate", "selector": "div.movie-thumbnail", "value": "", "expected": {}}, {"action": "verify", "selector": "div.movie-thumbnail", "value": "", "expected": {"property": "count", "value": "5", "relation": "&gt;="}}, {"action": "locate", "selector": "all input fields", "value": "", "expected": {}}, {"action": "verify", "selector": "all input fields", "value": "", "expected": {"property": "font-family", "value": "Roboto", "relation": ""}}, {"action": "verify", "selector": "all input fields", "value": "", "expected": {"property": "font-size", "value": "16px", "relation": ""}}, {"action": "locate", "selector": "all input fields", "value": "", "expected": {}}, {"action": "verify", "selector": "input field", "value": "", "expected": {"property": "padding", "value": "12px", "relation": ""}}, {"action": "locate", "selector": "input[type='text'], input[type='email'], input[type='password'], input[type='number'], textarea", "value": "", "expected": {}}, {"action": "verify", "selector": "all located input fields", "value": "", "expected": {"property": "margin-bottom", "value": "16px", "relation": "equal"}}, {"action": "verify", "selector": "'Sign In' button", "value": "", "expected": {"property": "background-color", "value": "#e50914", "relation": ""}}, {"action": "verify", "selector": "'Sign In' button", "value": "", "expected": {"property": "color", "value": "#ffffff", "relation": ""}}, {"action": "locate", "selector": "button with text 'Sign In'", "value": "", "expected": {}}, {"action": "verify", "selector": "button with text 'Sign In'", "value": "", "expected": {"property": "border-radius", "value": "4px", "relation": ""}}, {"action": "locate", "selector": "Sign In button", "value": "", "expected": {}}, {"action": "verify", "selector": "Sign In button", "value": "", "expected": {"property": "width", "value": "360px", "relation": "less than or equal to"}}, {"action": "locate", "selector": "body", "value": "", "expected": {}}, {"action": "verify", "selector": "all elements", "value": "", "expected": {"property": "contrast ratio", "value": "4.5:1", "relation": "at least"}}]</t>
+          <t>[{"action": "interact", "selector": "", "value": "https://www.netflix.com", "expected": {}}, {"action": "interact", "selector": "'Sign In' button at top-right corner (within 50px from top and 30px from right)", "value": "", "expected": {}}, {"action": "interact", "selector": "email input field", "value": "testuser@example.com", "expected": {}}, {"action": "interact", "selector": "password input field", "value": "Test@1234", "expected": {}}, {"action": "interact", "selector": "'login form'", "value": "", "expected": {}}, {"action": "verify", "selector": "", "value": "", "expected": {"dynamics": {"navigation": "https://www.netflix.com/browse", "timeout": "3 seconds"}}}, {"action": "verify", "selector": "personalized movie thumbnails", "value": "", "expected": {"count": {"min": 5}}}, {"action": "verify", "selector": "input", "value": "", "expected": {"styles": {"font": {"family": "Roboto", "size": "16px"}, "padding": {"top": "12px", "right": "12px", "bottom": "12px", "left": "12px"}, "margin": {"bottom": "16px"}}}}, {"action": "verify", "selector": "'Sign In' button", "value": "", "expected": {"styles": {"backgroundColor": "#e50914", "color": "#ffffff", "border": {"radius": "4px"}}}}, {"action": "verify", "selector": "'Sign In' button", "value": "", "expected": {"isResponsive": true, "atScreenWidth": "360px"}}, {"action": "verify", "selector": "all visible elements", "value": "", "expected": {"styles": {"contrastRatio": "&gt;= 4.5:1"}}}]</t>
         </is>
       </c>
     </row>
@@ -470,12 +470,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>["Open 'https://www.amazon.com'", "Fill 'Bluetooth speaker' into the search input", "Click the search button", "Verify that the search completes in under 2 seconds", "Verify that at least 10 products are displayed", "Verify that each product title contains the word 'Bluetooth'", "Verify that each product card has image width exactly '150px'", "Verify that each product card has price font-size '18px'", "Verify that the 'Add to Cart' button has color '#ff9900'", "Verify that the 'Add to Cart' button has rounded corners of '4px'", "Verify that the 'Add to Cart' button's hover background color changes to '#e68a00'"]</t>
+          <t>["Open 'https://www.amazon.com'", "Search for 'Bluetooth speaker'", "Verify that the search completes in under 2 seconds", "Verify that the search results display at least 10 products with titles containing the word 'Bluetooth'", "Verify that each product card has an image with width exactly '150px'", "Verify that the price on each product card has font-size '18px'", "Verify that the 'Add to Cart' button has color '#ff9900' and rounded corners of '4px'", "Verify that the 'Add to Cart' button's background color changes to '#e68a00' on hover"]</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>[{"action": "interact", "selector": "Search Amazon", "value": "https://www.amazon.com", "expected": {}}, {"action": "locate", "selector": "input[type='search']", "value": "", "expected": {}}, {"action": "interact", "selector": "input[type='search']", "value": "Bluetooth speaker", "expected": {}}, {"action": "locate", "selector": "button with text 'Search'", "value": "", "expected": {}}, {"action": "interact", "selector": "button with text 'Search'", "value": "", "expected": {}}, {"action": "locate", "selector": "input with placeholder 'Search'", "value": "", "expected": {}}, {"action": "interact", "selector": "input with placeholder 'Search'", "value": "test query", "expected": {}}, {"action": "locate", "selector": "button with text 'Search'", "value": "", "expected": {}}, {"action": "interact", "selector": "button with text 'Search'", "value": "", "expected": {}}, {"action": "verify", "selector": "results container", "value": "", "expected": {"property": "performance", "value": "2s", "relation": "less than"}}, {"action": "locate", "selector": "section containing products", "value": "", "expected": {}}, {"action": "verify", "selector": "product listing element", "value": "", "expected": {"property": "count", "value": "10", "relation": "greater than or equal to"}}, {"action": "locate", "selector": "all elements with tag 'h2'", "value": "", "expected": {}}, {"action": "verify", "selector": "all elements with tag 'h2'", "value": "", "expected": {"property": "text", "value": "Bluetooth", "relation": "contains"}}, {"action": "locate", "selector": "div[class*='product-card']", "value": "", "expected": {}}, {"action": "verify", "selector": "img", "value": "", "expected": {"property": "width", "value": "150px", "relation": "equal"}}, {"action": "locate", "selector": "div[class*='product-card']", "value": "", "expected": {}}, {"action": "verify", "selector": "div[class*='product-card']", "value": "", "expected": {"property": "font-size", "value": "18px", "relation": "equal"}}, {"action": "locate", "selector": "button with text 'Add to Cart'", "value": "", "expected": {}}, {"action": "verify", "selector": "button with text 'Add to Cart'", "value": "", "expected": {"property": "color", "value": "#ff9900", "relation": ""}}, {"action": "locate", "selector": "button with text 'Add to Cart'", "value": "", "expected": {}}, {"action": "verify", "selector": "button with text 'Add to Cart'", "value": "", "expected": {"property": "border-radius", "value": "4px", "relation": ""}}, {"action": "locate", "selector": "button with text 'Add to Cart'", "value": "", "expected": {}}, {"action": "interact", "selector": "button with text 'Add to Cart'", "value": "", "expected": {}}, {"action": "verify", "selector": "button with text 'Add to Cart'", "value": "", "expected": {"property": "background-color", "value": "#e68a00", "relation": ""}}]</t>
+          <t>[{"action": "interact", "selector": "", "value": "https://www.amazon.com", "expected": {"dynamics": {"navigation": "https://www.amazon.com"}}}, {"action": "interact", "selector": "search input field", "value": "Bluetooth speaker", "expected": {}}, {"action": "verify", "selector": "search results section", "value": "", "expected": {"dynamics": {"completionTime": "under 2 seconds"}}}, {"action": "verify", "selector": "search result product titles", "value": "", "expected": {"count": "&gt;= 10", "text": "contains 'Bluetooth'"}}, {"action": "verify", "selector": ".product-card img", "value": "", "expected": {"styles": {"width": "150px"}}}, {"action": "verify", "selector": ".product-card .price", "value": "", "expected": {"styles": {"font": {"size": "18px"}}}}, {"action": "verify", "selector": "'Add to Cart' button", "value": "", "expected": {"styles": {"color": "#ff9900", "border": {"radius": "4px"}}}}, {"action": "verify", "selector": "'Add to Cart' button", "value": "", "expected": {"state": {"hovered": true}, "styles": {"backgroundColor": "#e68a00"}}}]</t>
         </is>
       </c>
     </row>
@@ -487,12 +487,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>["Open 'https://www.khanacademy.org'", "Click on the 'Sign up' button", "Fill 'Jane Doe' into Name field", "Fill 'jane.doe@example.com' into Email field", "Fill 'Test1234@' into Password field", "Submit the form", "Confirm that the user is redirected to 'https://www.khanacademy.org/profile/me' within 2 seconds", "Check that the profile picture placeholder is a circle with diameter '100px'", "Check that the font used in the welcome message is 'Open Sans 20px bold'", "Check that all form fields support keyboard navigation", "Check that all form fields show red borders '#ff0000' on invalid input"]</t>
+          <t>["Open 'https://www.khanacademy.org'", "Click on the 'Sign up' button at the top-right", "Fill 'Jane Doe' into the name input field", "Fill 'jane.doe@example.com' into the email input field", "Fill 'Test1234@' into the password input field", "Submit the form", "Confirm that the user is redirected to 'https://www.khanacademy.org/profile/me' within 2 seconds", "Verify that the profile picture placeholder is a circle with diameter '100px'", "Verify that the font used in the welcome message is 'Open Sans 20px bold'", "Verify that all form fields support keyboard navigation", "Verify that all form fields show red borders '#ff0000' on invalid input"]</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>[{"action": "interact", "selector": "URL input", "value": "https://www.khanacademy.org", "expected": {}}, {"action": "interact", "selector": "Go button", "value": "", "expected": {}}, {"action": "assert", "selector": "page title", "value": "", "expected": {"property": "text", "value": "Khan Academy", "relation": "equal"}}, {"action": "interact", "selector": "button with text 'Sign up'", "value": "", "expected": {}}, {"action": "locate", "selector": "input field with label 'Name'", "value": "", "expected": {}}, {"action": "interact", "selector": "input field with label 'Name'", "value": "Jane Doe", "expected": {}}, {"action": "verify", "selector": "input field with label 'Name'", "value": "", "expected": {"property": "value", "value": "Jane Doe", "relation": "equal"}}, {"action": "interact", "selector": "input with label 'Email'", "value": "jane.doe@example.com", "expected": {}}, {"action": "locate", "selector": "Password field", "value": "", "expected": {}}, {"action": "interact", "selector": "Password field", "value": "Test1234@", "expected": {}}, {"action": "locate", "selector": "button[type='submit']", "value": "", "expected": {}}, {"action": "interact", "selector": "button[type='submit']", "value": "", "expected": {}}, {"action": "assert", "selector": "window location", "value": "", "expected": {"property": "href", "value": "https://www.khanacademy.org/profile/me", "relation": "includes"}}, {"action": "verify", "selector": "window", "value": "", "expected": {"property": "loadTime", "value": "2", "relation": "lessThanOrEqualTo"}}, {"action": "locate", "selector": "img[alt='Profile picture placeholder']", "value": "", "expected": {}}, {"action": "verify", "selector": "img[alt='Profile picture placeholder']", "value": "", "expected": {"property": "border-radius", "value": "50%", "relation": ""}}, {"action": "verify", "selector": "img[alt='Profile picture placeholder']", "value": "", "expected": {"property": "width", "value": "100px", "relation": ""}}, {"action": "verify", "selector": "img[alt='Profile picture placeholder']", "value": "", "expected": {"property": "height", "value": "100px", "relation": ""}}, {"action": "locate", "selector": "element with text 'Welcome!'", "value": "", "expected": {}}, {"action": "verify", "selector": "element with text 'Welcome!'", "value": "", "expected": {"property": "font-family", "value": "'Open Sans'", "relation": ""}}, {"action": "verify", "selector": "element with text 'Welcome!'", "value": "", "expected": {"property": "font-size", "value": "20px", "relation": ""}}, {"action": "verify", "selector": "element with text 'Welcome!'", "value": "", "expected": {"property": "font-weight", "value": "bold", "relation": ""}}, {"action": "locate", "selector": "first form field", "value": "", "expected": {}}, {"action": "interact", "selector": "first form field", "value": "", "expected": {}}, {"action": "verify", "selector": "first form field", "value": "", "expected": {"property": "isFocused", "value": "true", "relation": ""}}, {"action": "locate", "selector": "next form field", "value": "", "expected": {}}, {"action": "interact", "selector": "Tab key", "value": "", "expected": {}}, {"action": "verify", "selector": "second form field", "value": "", "expected": {"property": "isFocused", "value": "true", "relation": ""}}, {"action": "locate", "selector": "all form fields", "value": "", "expected": {}}, {"action": "verify", "selector": "all form fields", "value": "", "expected": {"property": "tabIndex", "value": "0", "relation": "equal"}}, {"action": "locate", "selector": "input field with label 'Username'", "value": "", "expected": {}}, {"action": "interact", "selector": "input field with label 'Username'", "value": "invalid_username", "expected": {}}, {"action": "verify", "selector": "input field with label 'Username'", "value": "", "expected": {"property": "border-color", "value": "#ff0000", "relation": ""}}, {"action": "locate", "selector": "input field with label 'Email'", "value": "", "expected": {}}, {"action": "interact", "selector": "input field with label 'Email'", "value": "invalid_email", "expected": {}}, {"action": "verify", "selector": "input field with label 'Email'", "value": "", "expected": {"property": "border-color", "value": "#ff0000", "relation": ""}}, {"action": "locate", "selector": "input field with label 'Password'", "value": "", "expected": {}}, {"action": "interact", "selector": "input field with label 'Password'", "value": "invalid_password", "expected": {}}, {"action": "verify", "selector": "input field with label 'Password'", "value": "", "expected": {"property": "border-color", "value": "#ff0000", "relation": ""}}]</t>
+          <t>[{"action": "interact", "selector": "", "value": "https://www.khanacademy.org", "expected": {}}, {"action": "interact", "selector": "'Sign up' button at the top-right", "value": "", "expected": {}}, {"action": "interact", "selector": "name input field", "value": "Jane Doe", "expected": {}}, {"action": "interact", "selector": "email input field", "value": "jane.doe@example.com", "expected": {}}, {"action": "interact", "selector": "password input field", "value": "Test1234@", "expected": {}}, {"action": "interact", "selector": "form submit button", "value": "", "expected": {}}, {"action": "verify", "selector": "", "value": "", "expected": {"dynamics": {"navigation": "https://www.khanacademy.org/profile/me"}}}, {"action": "verify", "selector": "profile picture placeholder", "value": "", "expected": {"styles": {"border": {"radius": "50%"}}, "position": {"width": 100, "height": 100}}}, {"action": "verify", "selector": "welcome message", "value": "", "expected": {"styles": {"font": {"family": "Open Sans", "size": "20px", "weight": "bold"}}}}, {"action": "verify", "selector": "form input, form select, form textarea", "value": "", "expected": {"state": {"enabled": true}, "dynamics": {"focus": true}}}, {"action": "verify", "selector": "form fields with invalid input", "value": "", "expected": {"styles": {"border": {"color": "#ff0000"}}}}]</t>
         </is>
       </c>
     </row>
@@ -504,12 +504,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>["Open 'https://web.whatsapp.com'", "Scan QR code", "Wait for contact list to load (max 5 seconds)", "Click on contact 'John Test'", "Type 'Hello from automation' into message input with height '40px' and font-size '14px'", "Click 'Send message' button", "Verify that sent message appears in chat bubble within 1 second", "Verify that chat bubble background color is '#dcf8c6'", "Verify that chat bubble is right aligned", "Verify that message timestamp is displayed in '12-hour' format", "Verify that message timestamp is aligned to the bottom-right inside the bubble"]</t>
+          <t>["Open 'https://web.whatsapp.com'", "Scan the QR code using test device", "Wait until the contact list loads (max 5 seconds)", "Click on a contact named 'John Test'", "Type 'Hello from automation' into the message input with height '40px' and font-size '14px'", "Send the message", "Verify that the sent message appears in the chat bubble within 1 second, with background color '#dcf8c6', right alignment, and message timestamp displayed in '12-hour' format aligned to the bottom-right inside the bubble"]</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>[{"action": "interact", "selector": "input[type='text']", "value": "https://web.whatsapp.com", "expected": {}}, {"action": "interact", "selector": "button[type='submit']", "value": "", "expected": {}}, {"action": "locate", "selector": "QR code scanner", "value": "", "expected": {}}, {"action": "interact", "selector": "QR code scanner", "value": "", "expected": {}}, {"action": "locate", "selector": "contact list", "value": "", "expected": {"property": "visibility", "value": "visible", "relation": ""}}, {"action": "assert", "selector": "contact list", "value": "", "expected": {"property": "load_time", "value": "5", "relation": "less than or equal to"}}, {"action": "locate", "selector": "contact with name 'John Test'", "value": "", "expected": {}}, {"action": "interact", "selector": "contact with name 'John Test'", "value": "", "expected": {}}, {"action": "locate", "selector": "input with placeholder 'Message'", "value": "", "expected": {}}, {"action": "verify", "selector": "input with placeholder 'Message'", "value": "", "expected": {"property": "height", "value": "40px", "relation": ""}}, {"action": "verify", "selector": "input with placeholder 'Message'", "value": "", "expected": {"property": "font-size", "value": "14px", "relation": ""}}, {"action": "interact", "selector": "input with placeholder 'Message'", "value": "Hello from automation", "expected": {}}, {"action": "locate", "selector": "button with text 'Send message'", "value": "", "expected": {}}, {"action": "interact", "selector": "button with text 'Send message'", "value": "", "expected": {}}, {"action": "locate", "selector": "input field for message", "value": "", "expected": {}}, {"action": "interact", "selector": "input field for message", "value": "Hello", "expected": {}}, {"action": "locate", "selector": "button with text 'Send'", "value": "", "expected": {}}, {"action": "interact", "selector": "button with text 'Send'", "value": "", "expected": {}}, {"action": "assert", "selector": "chat bubble containing 'Hello'", "value": "", "expected": {"property": "visibility", "value": "visible", "relation": ""}}, {"action": "verify", "selector": "chat bubble containing 'Hello'", "value": "", "expected": {"property": "text", "value": "Hello", "relation": ""}}, {"action": "verify", "selector": "chat bubble containing 'Hello'", "value": "", "expected": {"property": "timestamp", "value": "within 1 second", "relation": ""}}, {"action": "locate", "selector": "chat bubble", "value": "", "expected": {}}, {"action": "verify", "selector": "chat bubble", "value": "", "expected": {"property": "background-color", "value": "#dcf8c6", "relation": "equal"}}, {"action": "locate", "selector": "chat bubble", "value": "", "expected": {}}, {"action": "verify", "selector": "chat bubble", "value": "", "expected": {"property": "alignment", "value": "right", "relation": ""}}, {"action": "locate", "selector": "message timestamp", "value": "", "expected": {}}, {"action": "verify", "selector": "message timestamp", "value": "", "expected": {"property": "text", "value": "([1-9]|10|11|12):[0-5][0-9] ?(AM|PM)", "relation": ""}}, {"action": "locate", "selector": "bubble", "value": "", "expected": {}}, {"action": "locate", "selector": "message timestamp", "value": "", "expected": {"property": "position", "value": "bottom-right", "relation": "inside"}}, {"action": "verify", "selector": "message timestamp", "value": "", "expected": {"property": "alignment", "value": "bottom-right", "relation": "inside"}}]</t>
+          <t>[{"action": "interact", "selector": "", "value": "https://web.whatsapp.com", "expected": {"navigation": "https://web.whatsapp.com"}}, {"action": "interact", "selector": "QR code scanner", "value": "", "expected": {}}, {"action": "assert", "selector": "contact list", "value": "", "expected": {"state": {"visibility": "visible"}, "dynamics": {"loading": "none"}}}, {"action": "interact", "selector": "contact named 'John Test'", "value": "", "expected": {}}, {"action": "interact", "selector": "message input", "value": "Hello from automation", "expected": {"styles": {"height": "40px", "font": {"size": "14px"}}}}, {"action": "interact", "selector": "Send button", "value": "", "expected": {}}, {"action": "verify", "selector": "the sent message chat bubble", "value": "", "expected": {"state": {"visibility": "visible"}, "styles": {"backgroundColor": "#dcf8c6", "textAlign": "right"}}}]</t>
         </is>
       </c>
     </row>
@@ -521,12 +521,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>["Open 'https://my.clinicportal.com'", "Fill 'patient001' into Username field", "Fill 'Health@2023' into Password field", "Click on the 'Appointments' tab in the left-side menu with width '220px' and background '#f0f0f0'", "Verify the table of upcoming appointments shows at least 3 rows", "Verify each row in the table of upcoming appointments has font-size '15px'", "Verify the table of upcoming appointments has alternating row colors '#ffffff' and '#f9f9f9'", "Verify the 'Cancel' buttons are red '#d9534f' with white text", "Verify 'Cancel' buttons appear only for appointments scheduled at least 24 hours in the future"]</t>
+          <t>["Open 'https://my.clinicportal.com'", "Fill 'patient001' into the username input field", "Fill 'Health@2023' into the password input field", "Submit the login form", "Click on the 'Appointments' tab", "Verify the left-side menu has width '220px' and background '#f0f0f0'", "Verify the table of upcoming appointments shows at least 3 rows, each with font-size '15px', and alternating row colors '#ffffff' and '#f9f9f9'", "Verify 'Cancel' buttons are red '#d9534f' with white text and appear only for appointments scheduled at least 24 hours in the future"]</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>[{"action": "interact", "selector": "url 'https://my.clinicportal.com'", "value": "", "expected": {}}, {"action": "locate", "selector": "Username field", "value": "", "expected": {}}, {"action": "interact", "selector": "Username field", "value": "patient001", "expected": {}}, {"action": "locate", "selector": "Password", "value": "", "expected": {}}, {"action": "interact", "selector": "Password", "value": "Health@2023", "expected": {}}, {"action": "locate", "selector": "tab with text 'Appointments'", "value": "", "expected": {"property": "width", "value": "220px", "relation": ""}}, {"action": "verify", "selector": "tab with text 'Appointments'", "value": "", "expected": {"property": "background", "value": "#f0f0f0", "relation": ""}}, {"action": "interact", "selector": "tab with text 'Appointments'", "value": "", "expected": {}}, {"action": "locate", "selector": "table with id 'upcoming-appointments-table'", "value": "", "expected": {}}, {"action": "verify", "selector": "rows of table with id 'upcoming-appointments-table'", "value": "", "expected": {"property": "count", "value": "3", "relation": "greater than or equal to"}}, {"action": "locate", "selector": "table of upcoming appointments", "value": "", "expected": {}}, {"action": "verify", "selector": "each row in the table of upcoming appointments", "value": "", "expected": {"property": "font-size", "value": "15px", "relation": ""}}, {"action": "locate", "selector": "table with heading 'Upcoming Appointments'", "value": "", "expected": {}}, {"action": "verify", "selector": "row 1 of the table", "value": "", "expected": {"property": "background-color", "value": "#ffffff", "relation": ""}}, {"action": "verify", "selector": "row 2 of the table", "value": "", "expected": {"property": "background-color", "value": "#f9f9f9", "relation": ""}}, {"action": "verify", "selector": "row 3 of the table", "value": "", "expected": {"property": "background-color", "value": "#ffffff", "relation": ""}}, {"action": "verify", "selector": "row 4 of the table", "value": "", "expected": {"property": "background-color", "value": "#f9f9f9", "relation": ""}}, {"action": "locate", "selector": "button", "value": "", "expected": {"property": "text", "value": "Cancel", "relation": ""}}, {"action": "verify", "selector": "button[text='Cancel']", "value": "", "expected": {"property": "background-color", "value": "#d9534f", "relation": ""}}, {"action": "verify", "selector": "button[text='Cancel']", "value": "", "expected": {"property": "color", "value": "white", "relation": ""}}, {"action": "locate", "selector": "div", "value": "", "expected": {"property": "data-testid", "value": "appointment-list", "relation": ""}}, {"action": "locate", "selector": "div[data-testid='appointment-item']", "value": "", "expected": {}}, {"action": "verify", "selector": "button[data-testid='cancel-appointment']", "value": "", "expected": {"property": "visibility", "value": "hidden", "relation": ""}}, {"action": "locate", "selector": "div[data-testid='appointment-item']", "value": "", "expected": {"property": "attribute-value", "value": "future-appointment-24h+", "relation": "contains"}}, {"action": "verify", "selector": "button[data-testid='cancel-appointment']", "value": "", "expected": {"property": "visibility", "value": "visible", "relation": ""}}, {"action": "locate", "selector": "div[data-testid='appointment-item']", "value": "", "expected": {"property": "attribute-value", "value": "future-appointment-&lt;24h", "relation": "contains"}}, {"action": "verify", "selector": "button[data-testid='cancel-appointment']", "value": "", "expected": {"property": "visibility", "value": "hidden", "relation": ""}}]</t>
+          <t>[{"action": "interact", "selector": "", "value": "https://my.clinicportal.com", "expected": {}}, {"action": "interact", "selector": "username input field", "value": "patient001", "expected": {}}, {"action": "interact", "selector": "password input field", "value": "Health@2023", "expected": {}}, {"action": "interact", "selector": "'Login' button", "value": "", "expected": {}}, {"action": "interact", "selector": "'Appointments' tab", "value": "", "expected": {}}, {"action": "verify", "selector": "left-side menu", "value": "", "expected": {"styles": {"width": "220px", "backgroundColor": "#f0f0f0"}}}, {"action": "verify", "selector": "table of upcoming appointments tr", "value": "", "expected": {"minCount": 3, "styles": {"font": {"size": "15px"}}, "alternatingStyles": [{"backgroundColor": "#ffffff"}, {"backgroundColor": "#f9f9f9"}]}}, {"action": "verify", "selector": "'Cancel' button for an appointment scheduled at least 24 hours in the future", "value": "", "expected": {"text": "Cancel", "styles": {"backgroundColor": "#d9534f", "color": "white"}, "state": {"visibility": "visible"}}}]</t>
         </is>
       </c>
     </row>
@@ -538,12 +538,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>["Open 'https://www.booking.com'", "Fill 'Tokyo' into destination input", "Select check-in date '2025-09-01'", "Select check-out date '2025-09-07'", "Select '2 adults'", "Click search button", "Confirm result page loads within 4 seconds", "Confirm at least 5 hotels displayed", "Confirm 'Free Cancellation' badge is present on hotel cards", "Confirm hotel card width is '320px'", "Confirm image height is '180px'", "Confirm rating star icons have color '#febb02'", "Confirm 'Book Now' buttons are sticky on mobile view", "Confirm 'Book Now' buttons have minimum touch size '48x48px'"]</t>
+          <t>["Open 'https://www.booking.com'", "Input 'Tokyo' into the destination field", "Select '2025-09-01' as the check-in date", "Select '2025-09-07' as the check-out date", "Select '2 adults' for the number of guests", "Submit the search form", "Verify that the search results page loads within 4 seconds", "Verify that the page displays at least 5 hotels with the 'Free Cancellation' badge", "Verify that hotel cards have a width of '320px', an image height of '180px', and rating star icons in color '#febb02'", "Verify that the 'Book Now' buttons are sticky on mobile view and have a minimum touch size of '48x48px'"]</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>[{"action": "interact", "selector": "input[type='text']", "value": "https://www.booking.com", "expected": {}}, {"action": "interact", "selector": "button[type='submit']", "value": "", "expected": {}}, {"action": "locate", "selector": "input with placeholder 'Destination'", "value": "", "expected": {}}, {"action": "interact", "selector": "input with placeholder 'Destination'", "value": "Tokyo", "expected": {}}, {"action": "verify", "selector": "input with placeholder 'Destination'", "value": "", "expected": {"property": "value", "value": "Tokyo", "relation": ""}}, {"action": "locate", "selector": "element with id 'check-in-date-picker'", "value": "", "expected": {}}, {"action": "interact", "selector": "button with text 'September'", "value": "", "expected": {}}, {"action": "interact", "selector": "button with text '2025'", "value": "", "expected": {}}, {"action": "interact", "selector": "button with text '1'", "value": "", "expected": {}}, {"action": "verify", "selector": "input with id 'check-in-date'", "value": "2025-09-01", "expected": {"property": "value", "value": "2025-09-01", "relation": ""}}, {"action": "locate", "selector": "date picker input", "value": "", "expected": {}}, {"action": "interact", "selector": "date picker input", "value": "2025-09-07", "expected": {}}, {"action": "verify", "selector": "date picker input with value 2025-09-07", "value": "", "expected": {"property": "value", "value": "2025-09-07", "relation": "equal"}}, {"action": "locate", "selector": "button with text '2 adults'", "value": "", "expected": {}}, {"action": "interact", "selector": "button with text '2 adults'", "value": "", "expected": {}}, {"action": "interact", "selector": "button with text 'Search'", "value": "", "expected": {}}, {"action": "assert", "selector": "result page", "value": "", "expected": {"property": "visibility", "value": "visible", "relation": ""}}, {"action": "verify", "selector": "result page", "value": "", "expected": {"property": "load time", "value": "4s", "relation": "less than"}}, {"action": "locate", "selector": "hotel listing", "value": "", "expected": {}}, {"action": "verify", "selector": "number of located elements", "value": "", "expected": {"property": "count", "value": "5", "relation": "&gt;="}}, {"action": "locate", "selector": "hotel cards", "value": "", "expected": {}}, {"action": "assert", "selector": "badge with text 'Free Cancellation'", "value": "", "expected": {"property": "visibility", "value": "visible", "relation": ""}}, {"action": "locate", "selector": "card element representing a hotel", "value": "", "expected": {}}, {"action": "verify", "selector": "the located hotel card", "value": "", "expected": {"property": "width", "value": "320px", "relation": "equal"}}, {"action": "locate", "selector": "image", "value": "", "expected": {}}, {"action": "verify", "selector": "", "value": "", "expected": {"property": "height", "value": "180px", "relation": "equal"}}, {"action": "locate", "selector": "rating star icons", "value": "", "expected": {}}, {"action": "verify", "selector": "rating star icons", "value": "", "expected": {"property": "color", "value": "#febb02", "relation": ""}}, {"action": "locate", "selector": "body", "value": "", "expected": {}}, {"action": "verify", "selector": "button with text 'Book Now'", "value": "", "expected": {"property": "position", "value": "sticky", "relation": ""}}, {"action": "interact", "selector": "body", "value": "", "expected": {"property": "scroll", "value": "down", "relation": "by 500px"}}, {"action": "verify", "selector": "button with text 'Book Now'", "value": "", "expected": {"property": "position", "value": "sticky", "relation": ""}}, {"action": "locate", "selector": "button with text 'Book Now'", "value": "", "expected": {}}, {"action": "verify", "selector": "button with text 'Book Now'", "value": "", "expected": {"property": "width", "value": "48px", "relation": "&gt;="}}, {"action": "verify", "selector": "button with text 'Book Now'", "value": "", "expected": {"property": "height", "value": "48px", "relation": "&gt;="}}]</t>
+          <t>[{"action": "interact", "selector": "", "value": "https://www.booking.com", "expected": {}}, {"action": "interact", "selector": "destination field", "value": "Tokyo", "expected": {}}, {"action": "interact", "selector": "'check-in date' field", "value": "2025-09-01", "expected": {}}, {"action": "interact", "selector": "'check-out date' field", "value": "2025-09-07", "expected": {}}, {"action": "interact", "selector": "number of guests field", "value": "2 adults", "expected": {}}, {"action": "interact", "selector": "form button[type='submit'], input[type='submit']", "value": "", "expected": {}}, {"action": "verify", "selector": "search results page", "value": "", "expected": {"dynamics": {"loadTime": "&lt;= 4s"}}}, {"action": "verify", "selector": "hotel listing element containing 'Free Cancellation' badge", "value": "", "expected": {"count": {"operator": "greaterThanOrEqual", "value": 5}}}, {"action": "verify", "selector": "hotel cards", "value": "", "expected": {"position": {"width": "320px"}}}, {"action": "verify", "selector": "image within hotel cards", "value": "", "expected": {"position": {"height": "180px"}}}, {"action": "verify", "selector": "rating star icons", "value": "", "expected": {"styles": {"color": "#febb02"}}}, {"action": "verify", "selector": "'Book Now' buttons", "value": "", "expected": {"dynamics": {"scroll": "sticky"}, "position": {"minWidth": "48px", "minHeight": "48px"}}}]</t>
         </is>
       </c>
     </row>

--- a/Report/text002.summary.xlsx
+++ b/Report/text002.summary.xlsx
@@ -458,7 +458,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>[{"action": "interact", "selector": "", "value": "https://www.netflix.com", "expected": {}}, {"action": "interact", "selector": "'Sign In' button at top-right corner (within 50px from top and 30px from right)", "value": "", "expected": {}}, {"action": "interact", "selector": "email input field", "value": "testuser@example.com", "expected": {}}, {"action": "interact", "selector": "password input field", "value": "Test@1234", "expected": {}}, {"action": "interact", "selector": "'login form'", "value": "", "expected": {}}, {"action": "verify", "selector": "", "value": "", "expected": {"dynamics": {"navigation": "https://www.netflix.com/browse", "timeout": "3 seconds"}}}, {"action": "verify", "selector": "personalized movie thumbnails", "value": "", "expected": {"count": {"min": 5}}}, {"action": "verify", "selector": "input", "value": "", "expected": {"styles": {"font": {"family": "Roboto", "size": "16px"}, "padding": {"top": "12px", "right": "12px", "bottom": "12px", "left": "12px"}, "margin": {"bottom": "16px"}}}}, {"action": "verify", "selector": "'Sign In' button", "value": "", "expected": {"styles": {"backgroundColor": "#e50914", "color": "#ffffff", "border": {"radius": "4px"}}}}, {"action": "verify", "selector": "'Sign In' button", "value": "", "expected": {"isResponsive": true, "atScreenWidth": "360px"}}, {"action": "verify", "selector": "all visible elements", "value": "", "expected": {"styles": {"contrastRatio": "&gt;= 4.5:1"}}}]</t>
+          <t>[{"action": "interact", "selector": "", "value": "https://www.netflix.com", "expected": {"navigation": "https://www.netflix.com"}}, {"action": "interact", "selector": "'Sign In' button located at the top-right corner (within 50px from top and 30px from right)", "value": "", "expected": {}}, {"action": "interact", "selector": "email input field", "value": "testuser@example.com", "expected": {}}, {"action": "interact", "selector": "password input field", "value": "Test@1234", "expected": {}}, {"action": "interact", "selector": "login form", "value": "", "expected": {}}, {"action": "verify", "selector": "", "value": "", "expected": {"dynamics": {"navigation": "https://www.netflix.com/browse", "timeout": "3 seconds"}}}, {"action": "verify", "selector": "personalized movie thumbnails", "value": "", "expected": {"count": {"min": 5}}}, {"action": "verify", "selector": "input", "value": "", "expected": {"styles": {"font": {"family": "Roboto", "size": "16px"}, "padding": {"top": "12px", "right": "12px", "bottom": "12px", "left": "12px"}, "margin": {"bottom": "16px"}}}}, {"action": "verify", "selector": "'Sign In' button", "value": "", "expected": {"styles": {"backgroundColor": "#e50914", "color": "#ffffff", "border": {"radius": "4px"}}}}, {"action": "verify", "selector": "'Sign In' button", "value": "", "expected": {"screenWidth": "360px", "state": {"visibility": "visible", "enabled": true}}}, {"action": "verify", "selector": "all visible elements", "value": "", "expected": {"accessibility": {"contrastRatio": "at least 4.5:1"}}}]</t>
         </is>
       </c>
     </row>
@@ -470,12 +470,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>["Open 'https://www.amazon.com'", "Search for 'Bluetooth speaker'", "Verify that the search completes in under 2 seconds", "Verify that the search results display at least 10 products with titles containing the word 'Bluetooth'", "Verify that each product card has an image with width exactly '150px'", "Verify that the price on each product card has font-size '18px'", "Verify that the 'Add to Cart' button has color '#ff9900' and rounded corners of '4px'", "Verify that the 'Add to Cart' button's background color changes to '#e68a00' on hover"]</t>
+          <t>["Open 'https://www.amazon.com'", "Search for 'Bluetooth speaker'", "Verify that the search completes in under 2 seconds", "Verify that the search results display at least 10 products with titles containing the word 'Bluetooth'", "Verify that each product card has an image with width exactly '150px' and a price with font-size '18px'", "Verify that the 'Add to Cart' button has color '#ff9900' and rounded corners of '4px'", "Verify that the 'Add to Cart' button's background color changes to '#e68a00' on hover"]</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>[{"action": "interact", "selector": "", "value": "https://www.amazon.com", "expected": {"dynamics": {"navigation": "https://www.amazon.com"}}}, {"action": "interact", "selector": "search input field", "value": "Bluetooth speaker", "expected": {}}, {"action": "verify", "selector": "search results section", "value": "", "expected": {"dynamics": {"completionTime": "under 2 seconds"}}}, {"action": "verify", "selector": "search result product titles", "value": "", "expected": {"count": "&gt;= 10", "text": "contains 'Bluetooth'"}}, {"action": "verify", "selector": ".product-card img", "value": "", "expected": {"styles": {"width": "150px"}}}, {"action": "verify", "selector": ".product-card .price", "value": "", "expected": {"styles": {"font": {"size": "18px"}}}}, {"action": "verify", "selector": "'Add to Cart' button", "value": "", "expected": {"styles": {"color": "#ff9900", "border": {"radius": "4px"}}}}, {"action": "verify", "selector": "'Add to Cart' button", "value": "", "expected": {"state": {"hovered": true}, "styles": {"backgroundColor": "#e68a00"}}}]</t>
+          <t>[{"action": "interact", "selector": "", "value": "https://www.amazon.com", "expected": {}}, {"action": "interact", "selector": "'Search' input field", "value": "Bluetooth speaker", "expected": {}}, {"action": "verify", "selector": "search results", "value": "", "expected": {"state": {"visibility": "visible"}, "dynamics": {"duration": "&lt;2s"}}}, {"action": "verify", "selector": ".search-results .product-title", "value": "", "expected": {"count": {"min": 10}, "text": {"contains": "Bluetooth"}}}, {"action": "verify", "selector": "'product card'", "value": "", "expected": {"descendantProperties": {"img": {"styles": {"width": "150px"}}, ".price": {"styles": {"font": {"size": "18px"}}}}}}, {"action": "verify", "selector": "'Add to Cart' button", "value": "", "expected": {"styles": {"color": "#ff9900", "border": {"radius": "4px"}}}}, {"action": "verify", "selector": "'Add to Cart' button", "value": "", "expected": {"state": {"hovered": true}, "styles": {"backgroundColor": "#e68a00"}}}]</t>
         </is>
       </c>
     </row>
@@ -492,7 +492,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>[{"action": "interact", "selector": "", "value": "https://www.khanacademy.org", "expected": {}}, {"action": "interact", "selector": "'Sign up' button at the top-right", "value": "", "expected": {}}, {"action": "interact", "selector": "name input field", "value": "Jane Doe", "expected": {}}, {"action": "interact", "selector": "email input field", "value": "jane.doe@example.com", "expected": {}}, {"action": "interact", "selector": "password input field", "value": "Test1234@", "expected": {}}, {"action": "interact", "selector": "form submit button", "value": "", "expected": {}}, {"action": "verify", "selector": "", "value": "", "expected": {"dynamics": {"navigation": "https://www.khanacademy.org/profile/me"}}}, {"action": "verify", "selector": "profile picture placeholder", "value": "", "expected": {"styles": {"border": {"radius": "50%"}}, "position": {"width": 100, "height": 100}}}, {"action": "verify", "selector": "welcome message", "value": "", "expected": {"styles": {"font": {"family": "Open Sans", "size": "20px", "weight": "bold"}}}}, {"action": "verify", "selector": "form input, form select, form textarea", "value": "", "expected": {"state": {"enabled": true}, "dynamics": {"focus": true}}}, {"action": "verify", "selector": "form fields with invalid input", "value": "", "expected": {"styles": {"border": {"color": "#ff0000"}}}}]</t>
+          <t>[{"action": "interact", "selector": "", "value": "https://www.khanacademy.org", "expected": {}}, {"action": "interact", "selector": "'Sign up' button at the top-right", "value": "", "expected": {}}, {"action": "interact", "selector": "name input field", "value": "Jane Doe", "expected": {}}, {"action": "interact", "selector": "email input field", "value": "jane.doe@example.com", "expected": {}}, {"action": "interact", "selector": "password input field", "value": "Test1234@", "expected": {}}, {"action": "interact", "selector": "submit button", "value": "", "expected": {}}, {"action": "verify", "selector": "", "value": "", "expected": {"dynamics": {"navigation": "https://www.khanacademy.org/profile/me"}}}, {"action": "verify", "selector": "profile picture placeholder", "value": "", "expected": {"position": {"width": "100px", "height": "100px"}, "styles": {"border": {"radius": "50%"}}}}, {"action": "verify", "selector": "welcome message", "value": "", "expected": {"styles": {"font": {"family": "Open Sans", "size": "20px", "weight": "bold"}}}}, {"action": "verify", "selector": "all form fields", "value": "", "expected": {"dynamics": {"focus": true}}}, {"action": "verify", "selector": "input, textarea, select", "value": "", "expected": {"styles": {"border": {"color": "#ff0000"}}}}]</t>
         </is>
       </c>
     </row>
@@ -504,12 +504,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>["Open 'https://web.whatsapp.com'", "Scan the QR code using test device", "Wait until the contact list loads (max 5 seconds)", "Click on a contact named 'John Test'", "Type 'Hello from automation' into the message input with height '40px' and font-size '14px'", "Send the message", "Verify that the sent message appears in the chat bubble within 1 second, with background color '#dcf8c6', right alignment, and message timestamp displayed in '12-hour' format aligned to the bottom-right inside the bubble"]</t>
+          <t>["Open 'https://web.whatsapp.com'", "Scan the QR code using test device", "Wait until the contact list loads (max 5 seconds)", "Click on a contact named 'John Test'", "Verify that the message input has height '40px' and font-size '14px'", "Type 'Hello from automation' into the message input", "Send the message", "Verify that the sent message appears in the chat bubble within 1 second", "Verify that the sent message chat bubble has background color '#dcf8c6', is right aligned, and its timestamp is displayed in '12-hour' format and aligned to the bottom-right inside the bubble"]</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>[{"action": "interact", "selector": "", "value": "https://web.whatsapp.com", "expected": {"navigation": "https://web.whatsapp.com"}}, {"action": "interact", "selector": "QR code scanner", "value": "", "expected": {}}, {"action": "assert", "selector": "contact list", "value": "", "expected": {"state": {"visibility": "visible"}, "dynamics": {"loading": "none"}}}, {"action": "interact", "selector": "contact named 'John Test'", "value": "", "expected": {}}, {"action": "interact", "selector": "message input", "value": "Hello from automation", "expected": {"styles": {"height": "40px", "font": {"size": "14px"}}}}, {"action": "interact", "selector": "Send button", "value": "", "expected": {}}, {"action": "verify", "selector": "the sent message chat bubble", "value": "", "expected": {"state": {"visibility": "visible"}, "styles": {"backgroundColor": "#dcf8c6", "textAlign": "right"}}}]</t>
+          <t>[{"action": "interact", "selector": "", "value": "https://web.whatsapp.com", "expected": {}}, {"action": "interact", "selector": "", "value": "", "expected": {}}, {"action": "assert", "selector": "the contact list", "value": "", "expected": {"state": {"visibility": "visible"}}}, {"action": "interact", "selector": "contact named 'John Test'", "value": "", "expected": {}}, {"action": "verify", "selector": "message input", "value": "", "expected": {"position": {"height": "40px"}, "styles": {"font": {"size": "14px"}}}}, {"action": "interact", "selector": "message input", "value": "Hello from automation", "expected": {}}, {"action": "interact", "selector": "Send button", "value": "", "expected": {}}, {"action": "verify", "selector": "the chat bubble", "value": "", "expected": {"text": "the sent message", "state": {"visibility": "visible"}}}, {"action": "verify", "selector": "sent message chat bubble", "value": "", "expected": {"styles": {"backgroundColor": "#dcf8c6"}, "position": {"horizontalAlignment": "right"}, "timestampFormat": "12-hour", "timestampPosition": {"verticalAlignment": "bottom", "horizontalAlignment": "right"}}}]</t>
         </is>
       </c>
     </row>
@@ -521,12 +521,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>["Open 'https://my.clinicportal.com'", "Fill 'patient001' into the username input field", "Fill 'Health@2023' into the password input field", "Submit the login form", "Click on the 'Appointments' tab", "Verify the left-side menu has width '220px' and background '#f0f0f0'", "Verify the table of upcoming appointments shows at least 3 rows, each with font-size '15px', and alternating row colors '#ffffff' and '#f9f9f9'", "Verify 'Cancel' buttons are red '#d9534f' with white text and appear only for appointments scheduled at least 24 hours in the future"]</t>
+          <t>["Open 'https://my.clinicportal.com'", "Fill 'patient001' into the username input field", "Fill 'Health@2023' into the password input field", "Click on the 'Appointments' tab in the left-side menu which has width '220px' and background '#f0f0f0'", "Verify the table of upcoming appointments shows at least 3 rows", "Verify that each row in the appointments table has font-size '15px' and alternating row background colors '#ffffff' and '#f9f9f9'", "Verify that the 'Cancel' buttons are red '#d9534f' with white text", "Verify that 'Cancel' buttons appear only for appointments scheduled at least 24 hours in the future"]</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>[{"action": "interact", "selector": "", "value": "https://my.clinicportal.com", "expected": {}}, {"action": "interact", "selector": "username input field", "value": "patient001", "expected": {}}, {"action": "interact", "selector": "password input field", "value": "Health@2023", "expected": {}}, {"action": "interact", "selector": "'Login' button", "value": "", "expected": {}}, {"action": "interact", "selector": "'Appointments' tab", "value": "", "expected": {}}, {"action": "verify", "selector": "left-side menu", "value": "", "expected": {"styles": {"width": "220px", "backgroundColor": "#f0f0f0"}}}, {"action": "verify", "selector": "table of upcoming appointments tr", "value": "", "expected": {"minCount": 3, "styles": {"font": {"size": "15px"}}, "alternatingStyles": [{"backgroundColor": "#ffffff"}, {"backgroundColor": "#f9f9f9"}]}}, {"action": "verify", "selector": "'Cancel' button for an appointment scheduled at least 24 hours in the future", "value": "", "expected": {"text": "Cancel", "styles": {"backgroundColor": "#d9534f", "color": "white"}, "state": {"visibility": "visible"}}}]</t>
+          <t>[{"action": "interact", "selector": "", "value": "https://my.clinicportal.com", "expected": {}}, {"action": "interact", "selector": "username input field", "value": "patient001", "expected": {}}, {"action": "interact", "selector": "password input field", "value": "Health@2023", "expected": {}}, {"action": "interact", "selector": "'Appointments' tab in the left-side menu", "value": "", "expected": {"position": {"width": "220px"}, "styles": {"backgroundColor": "#f0f0f0"}}}, {"action": "verify", "selector": "rows of the table of upcoming appointments", "value": "", "expected": {"count": "&gt;= 3"}}, {"action": "verify", "selector": "each row in the appointments table", "value": "", "expected": {"styles": {"font": {"size": "15px"}, "backgroundColor": "alternating('#ffffff', '#f9f9f9')"}}}, {"action": "verify", "selector": "'Cancel' buttons", "value": "", "expected": {"styles": {"backgroundColor": "#d9534f", "color": "white"}}}, {"action": "verify", "selector": "'Cancel' buttons", "value": "", "expected": {"state": {"visibility": {"rule": "visible if associated appointment is scheduled at least 24 hours in the future, otherwise hidden"}}}}]</t>
         </is>
       </c>
     </row>
@@ -538,12 +538,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>["Open 'https://www.booking.com'", "Input 'Tokyo' into the destination field", "Select '2025-09-01' as the check-in date", "Select '2025-09-07' as the check-out date", "Select '2 adults' for the number of guests", "Submit the search form", "Verify that the search results page loads within 4 seconds", "Verify that the page displays at least 5 hotels with the 'Free Cancellation' badge", "Verify that hotel cards have a width of '320px', an image height of '180px', and rating star icons in color '#febb02'", "Verify that the 'Book Now' buttons are sticky on mobile view and have a minimum touch size of '48x48px'"]</t>
+          <t>["Open 'https://www.booking.com'", "Input 'Tokyo' into the destination field", "Select '2025-09-01' as the check-in date", "Select '2025-09-07' as the check-out date", "Select '2 adults'", "Submit the search", "Verify that the result page loads within 4 seconds", "Verify that the result page displays at least 5 hotels with 'Free Cancellation' badge", "Verify that hotel cards have a width of '320px'", "Verify that hotel image heights are '180px'", "Verify that rating star icons are color '#febb02'", "Verify that 'Book Now' buttons are sticky on mobile view and have a minimum touch size of '48x48px'"]</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>[{"action": "interact", "selector": "", "value": "https://www.booking.com", "expected": {}}, {"action": "interact", "selector": "destination field", "value": "Tokyo", "expected": {}}, {"action": "interact", "selector": "'check-in date' field", "value": "2025-09-01", "expected": {}}, {"action": "interact", "selector": "'check-out date' field", "value": "2025-09-07", "expected": {}}, {"action": "interact", "selector": "number of guests field", "value": "2 adults", "expected": {}}, {"action": "interact", "selector": "form button[type='submit'], input[type='submit']", "value": "", "expected": {}}, {"action": "verify", "selector": "search results page", "value": "", "expected": {"dynamics": {"loadTime": "&lt;= 4s"}}}, {"action": "verify", "selector": "hotel listing element containing 'Free Cancellation' badge", "value": "", "expected": {"count": {"operator": "greaterThanOrEqual", "value": 5}}}, {"action": "verify", "selector": "hotel cards", "value": "", "expected": {"position": {"width": "320px"}}}, {"action": "verify", "selector": "image within hotel cards", "value": "", "expected": {"position": {"height": "180px"}}}, {"action": "verify", "selector": "rating star icons", "value": "", "expected": {"styles": {"color": "#febb02"}}}, {"action": "verify", "selector": "'Book Now' buttons", "value": "", "expected": {"dynamics": {"scroll": "sticky"}, "position": {"minWidth": "48px", "minHeight": "48px"}}}]</t>
+          <t>[{"action": "interact", "selector": "", "value": "https://www.booking.com", "expected": {}}, {"action": "interact", "selector": "destination field", "value": "Tokyo", "expected": {}}, {"action": "interact", "selector": "check-in date field", "value": "2025-09-01", "expected": {}}, {"action": "interact", "selector": "'check-out date' input field", "value": "2025-09-07", "expected": {}}, {"action": "interact", "selector": "'2 adults'", "value": "", "expected": {}}, {"action": "interact", "selector": "'Search' button or 'Submit' button", "value": "", "expected": {}}, {"action": "verify", "selector": "the result page", "value": "", "expected": {"loadTime": "&lt;= 4s"}}, {"action": "verify", "selector": "hotel listings with 'Free Cancellation' badge", "value": "", "expected": {"minCount": 5}}, {"action": "verify", "selector": "'hotel cards'", "value": "", "expected": {"position": {"width": "320px"}}}, {"action": "verify", "selector": "img.hotel-image", "value": "", "expected": {"styles": {"height": "180px"}}}, {"action": "verify", "selector": "rating star icons", "value": "", "expected": {"styles": {"color": "#febb02"}}}, {"action": "verify", "selector": "'Book Now' buttons", "value": "", "expected": {"dynamics": {"scroll": "sticky"}, "position": {"minWidth": "48px", "minHeight": "48px"}}}]</t>
         </is>
       </c>
     </row>
